--- a/data/trans_dic/P15D$urgencias-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P15D$urgencias-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, acudir a urgencias</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, acudir a urgencias (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>34,37; 76,78</t>
+          <t>34,28; 75,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>54,97; 78,59</t>
+          <t>54,75; 78,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,27; 75,53</t>
+          <t>47,84; 76,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38,06; 68,28</t>
+          <t>38,46; 69,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45,92; 88,75</t>
+          <t>43,92; 88,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,03; 69,7</t>
+          <t>42,51; 70,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,33; 75,68</t>
+          <t>49,57; 77,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>41,05; 62,97</t>
+          <t>40,01; 61,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44,5; 75,57</t>
+          <t>44,25; 76,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53,9; 71,33</t>
+          <t>52,9; 71,25</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52,51; 72,75</t>
+          <t>52,27; 72,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,76; 62,74</t>
+          <t>42,85; 61,59</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>39,82; 70,17</t>
+          <t>38,85; 69,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,81; 74,85</t>
+          <t>52,42; 74,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43,76; 70,34</t>
+          <t>42,93; 69,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37,06; 66,08</t>
+          <t>36,38; 66,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,95; 76,88</t>
+          <t>39,83; 75,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,69; 65,79</t>
+          <t>40,43; 64,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,49; 68,89</t>
+          <t>37,83; 69,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,81; 59,66</t>
+          <t>35,61; 60,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>44,57; 68,43</t>
+          <t>44,35; 67,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50,17; 66,28</t>
+          <t>51,23; 67,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44,97; 65,52</t>
+          <t>45,86; 65,54</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,73; 60,67</t>
+          <t>39,5; 59,39</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,59; 32,34</t>
+          <t>3,5; 35,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43,87; 70,61</t>
+          <t>45,18; 70,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>49,96; 81,65</t>
+          <t>51,43; 82,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42,76; 79,54</t>
+          <t>43,3; 77,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>55,95; 90,87</t>
+          <t>53,01; 89,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,86; 76,34</t>
+          <t>51,89; 77,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,76; 81,09</t>
+          <t>45,45; 82,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>40,15; 65,75</t>
+          <t>39,29; 63,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31,16; 59,8</t>
+          <t>30,11; 60,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52,47; 70,13</t>
+          <t>52,52; 70,64</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>53,44; 77,9</t>
+          <t>54,1; 78,06</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>43,84; 66,78</t>
+          <t>44,91; 66,81</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,89; 68,33</t>
+          <t>33,26; 67,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,7; 57,66</t>
+          <t>37,36; 59,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45,93; 70,69</t>
+          <t>46,23; 72,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53,76; 79,49</t>
+          <t>54,42; 80,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,22; 77,65</t>
+          <t>36,36; 78,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,15; 59,31</t>
+          <t>35,61; 60,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,75; 85,16</t>
+          <t>60,31; 85,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>42,81; 62,19</t>
+          <t>42,13; 62,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40,2; 65,8</t>
+          <t>40,81; 67,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39,84; 55,89</t>
+          <t>39,85; 56,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>57,69; 75,02</t>
+          <t>56,9; 74,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>51,95; 67,83</t>
+          <t>51,76; 67,75</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,34; 55,33</t>
+          <t>37,74; 55,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>52,06; 64,07</t>
+          <t>52,57; 64,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53,48; 67,38</t>
+          <t>53,96; 67,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50,28; 66,3</t>
+          <t>50,95; 66,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>54,64; 74,35</t>
+          <t>54,77; 75,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,01; 62,1</t>
+          <t>49,35; 62,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,09; 71,8</t>
+          <t>57,57; 71,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>44,23; 56,89</t>
+          <t>44,81; 56,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>47,39; 60,8</t>
+          <t>46,8; 61,38</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52,43; 61,04</t>
+          <t>52,96; 61,54</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57,64; 67,45</t>
+          <t>58,11; 68,37</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>49,97; 59,18</t>
+          <t>50,05; 60,15</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, acudir a urgencias</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, acudir a urgencias (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7830; 17491</t>
+          <t>7810; 17194</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32444; 46386</t>
+          <t>32313; 46091</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19669; 31426</t>
+          <t>19904; 31644</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17080; 30643</t>
+          <t>17259; 31121</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7286; 14082</t>
+          <t>6968; 14098</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22053; 36577</t>
+          <t>22306; 36970</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23522; 36839</t>
+          <t>24128; 37788</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17752; 27231</t>
+          <t>17303; 26572</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17197; 29208</t>
+          <t>17102; 29667</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>60096; 79527</t>
+          <t>58987; 79446</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47408; 65680</t>
+          <t>47192; 65459</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37683; 55291</t>
+          <t>37761; 54274</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17034; 30020</t>
+          <t>16622; 29609</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40971; 59191</t>
+          <t>41454; 58865</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26467; 42539</t>
+          <t>25963; 42008</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24849; 44315</t>
+          <t>24398; 44327</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12040; 23168</t>
+          <t>12002; 22872</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29517; 47720</t>
+          <t>29329; 46578</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17776; 32663</t>
+          <t>17936; 32797</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19926; 34148</t>
+          <t>20383; 34689</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32495; 49892</t>
+          <t>32340; 49303</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>76067; 100496</t>
+          <t>77672; 101668</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48521; 70684</t>
+          <t>49482; 70704</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>49377; 75413</t>
+          <t>49094; 73817</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>854; 7698</t>
+          <t>833; 8420</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25207; 40571</t>
+          <t>25964; 40301</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18320; 29937</t>
+          <t>18856; 30191</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12501; 23253</t>
+          <t>12659; 22703</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13491; 21912</t>
+          <t>12784; 21560</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30151; 43548</t>
+          <t>29601; 43931</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15075; 25592</t>
+          <t>14344; 26155</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17708; 29001</t>
+          <t>17330; 27962</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14933; 28658</t>
+          <t>14428; 28940</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>60083; 80303</t>
+          <t>60137; 80893</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36460; 53146</t>
+          <t>36913; 53257</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32155; 48977</t>
+          <t>32940; 48998</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11086; 23033</t>
+          <t>11213; 22741</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32375; 50863</t>
+          <t>32957; 52492</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27964; 43041</t>
+          <t>28148; 44214</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>31658; 46808</t>
+          <t>32044; 47222</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8106; 18394</t>
+          <t>8612; 18707</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25411; 42871</t>
+          <t>25743; 43599</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37414; 53328</t>
+          <t>37763; 53340</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29545; 42919</t>
+          <t>29079; 42914</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23075; 37771</t>
+          <t>23424; 38529</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>63935; 89706</t>
+          <t>63951; 90924</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71244; 92647</t>
+          <t>70278; 92242</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>66446; 86752</t>
+          <t>66198; 86648</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>44731; 68097</t>
+          <t>46445; 68865</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>147737; 181822</t>
+          <t>149176; 181649</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>106766; 134514</t>
+          <t>107727; 135418</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>100593; 132643</t>
+          <t>101920; 132688</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>51253; 69745</t>
+          <t>51379; 70627</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>124644; 157938</t>
+          <t>125526; 158211</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>108617; 136617</t>
+          <t>109543; 136873</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>94485; 121523</t>
+          <t>95708; 120943</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>102779; 131867</t>
+          <t>101500; 133121</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>282136; 328442</t>
+          <t>284961; 331171</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>224745; 262987</t>
+          <t>226554; 266569</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>206704; 244820</t>
+          <t>207018; 248835</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15D$urgencias-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P15D$urgencias-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>54,08%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>34,28; 75,47</t>
+          <t>34,46; 75,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>54,75; 78,09</t>
+          <t>55,18; 79,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,84; 76,06</t>
+          <t>47,91; 75,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38,46; 69,34</t>
+          <t>40,08; 70,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,92; 88,85</t>
+          <t>45,66; 88,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,51; 70,45</t>
+          <t>44,0; 71,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,57; 77,63</t>
+          <t>47,27; 76,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40,01; 61,45</t>
+          <t>41,18; 62,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44,25; 76,76</t>
+          <t>45,06; 76,58</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52,9; 71,25</t>
+          <t>53,3; 71,11</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52,27; 72,5</t>
+          <t>53,27; 72,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,85; 61,59</t>
+          <t>44,45; 64,8</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>51,89%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,85; 69,21</t>
+          <t>39,38; 71,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52,42; 74,44</t>
+          <t>52,24; 75,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,93; 69,46</t>
+          <t>44,21; 70,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36,38; 66,1</t>
+          <t>39,64; 67,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,83; 75,9</t>
+          <t>38,11; 75,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,43; 64,21</t>
+          <t>40,97; 63,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,83; 69,17</t>
+          <t>39,57; 69,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,61; 60,61</t>
+          <t>35,2; 60,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>44,35; 67,62</t>
+          <t>43,73; 68,54</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51,23; 67,06</t>
+          <t>50,1; 66,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45,86; 65,54</t>
+          <t>46,12; 64,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,5; 59,39</t>
+          <t>42,23; 60,92</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>57,94%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,5; 35,37</t>
+          <t>3,93; 34,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45,18; 70,14</t>
+          <t>43,49; 70,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,43; 82,34</t>
+          <t>50,89; 82,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43,3; 77,66</t>
+          <t>46,81; 79,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>53,01; 89,41</t>
+          <t>55,42; 89,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51,89; 77,01</t>
+          <t>52,39; 78,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,45; 82,87</t>
+          <t>47,11; 82,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,29; 63,39</t>
+          <t>41,28; 66,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,11; 60,39</t>
+          <t>32,11; 59,72</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52,52; 70,64</t>
+          <t>51,92; 69,86</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54,1; 78,06</t>
+          <t>53,31; 77,14</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44,91; 66,81</t>
+          <t>46,45; 67,6</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>59,33%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,26; 67,46</t>
+          <t>33,27; 67,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,36; 59,51</t>
+          <t>36,34; 58,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,23; 72,62</t>
+          <t>46,13; 72,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54,42; 80,19</t>
+          <t>54,32; 78,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>36,36; 78,97</t>
+          <t>34,8; 77,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,61; 60,32</t>
+          <t>34,98; 59,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,31; 85,18</t>
+          <t>60,56; 83,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>42,13; 62,18</t>
+          <t>42,54; 62,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40,81; 67,12</t>
+          <t>39,96; 66,74</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39,85; 56,65</t>
+          <t>39,33; 56,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56,9; 74,69</t>
+          <t>57,29; 74,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>51,76; 67,75</t>
+          <t>50,4; 65,94</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>55,7%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>37,74; 55,95</t>
+          <t>37,08; 55,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>52,57; 64,01</t>
+          <t>51,59; 64,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53,96; 67,83</t>
+          <t>53,55; 67,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50,95; 66,32</t>
+          <t>52,38; 66,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>54,77; 75,29</t>
+          <t>54,18; 73,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,35; 62,2</t>
+          <t>48,52; 60,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,57; 71,94</t>
+          <t>57,41; 71,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>44,81; 56,62</t>
+          <t>45,89; 57,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>46,8; 61,38</t>
+          <t>47,78; 61,13</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52,96; 61,54</t>
+          <t>52,23; 61,31</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58,11; 68,37</t>
+          <t>57,67; 67,53</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,05; 60,15</t>
+          <t>50,82; 60,1</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24363</t>
+          <t>27706</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22153</t>
+          <t>24539</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>46516</t>
+          <t>52245</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7810; 17194</t>
+          <t>7850; 17113</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32313; 46091</t>
+          <t>32568; 46640</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19904; 31644</t>
+          <t>19936; 31228</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17259; 31121</t>
+          <t>19914; 35004</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6968; 14098</t>
+          <t>7245; 14066</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22306; 36970</t>
+          <t>23089; 37762</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24128; 37788</t>
+          <t>23010; 37464</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17303; 26572</t>
+          <t>19322; 29504</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17102; 29667</t>
+          <t>17416; 29596</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58987; 79446</t>
+          <t>59426; 79281</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47192; 65459</t>
+          <t>48093; 65318</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37761; 54274</t>
+          <t>42949; 62600</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34364</t>
+          <t>40556</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27231</t>
+          <t>30849</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>61594</t>
+          <t>71405</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16622; 29609</t>
+          <t>16846; 30638</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41454; 58865</t>
+          <t>41308; 59620</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25963; 42008</t>
+          <t>26737; 42630</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24398; 44327</t>
+          <t>29653; 50734</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12002; 22872</t>
+          <t>11484; 22840</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29329; 46578</t>
+          <t>29717; 46291</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17936; 32797</t>
+          <t>18762; 32795</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20383; 34689</t>
+          <t>22106; 38098</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32340; 49303</t>
+          <t>31888; 49977</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>77672; 101668</t>
+          <t>75960; 100948</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49482; 70704</t>
+          <t>49758; 69934</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>49094; 73817</t>
+          <t>58116; 83837</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18408</t>
+          <t>21358</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22713</t>
+          <t>26416</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41121</t>
+          <t>47773</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>833; 8420</t>
+          <t>936; 8222</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25964; 40301</t>
+          <t>24992; 40696</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18856; 30191</t>
+          <t>18660; 30115</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12659; 22703</t>
+          <t>15435; 26153</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12784; 21560</t>
+          <t>13364; 21533</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29601; 43931</t>
+          <t>29886; 44733</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14344; 26155</t>
+          <t>14867; 26035</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17330; 27962</t>
+          <t>20425; 32856</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14428; 28940</t>
+          <t>15387; 28617</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>60137; 80893</t>
+          <t>59449; 79995</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36913; 53257</t>
+          <t>36371; 52632</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32940; 48998</t>
+          <t>38302; 55737</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40623</t>
+          <t>42695</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>36165</t>
+          <t>38308</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>76788</t>
+          <t>81003</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11213; 22741</t>
+          <t>11215; 22734</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32957; 52492</t>
+          <t>32054; 51584</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28148; 44214</t>
+          <t>28088; 44215</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>32044; 47222</t>
+          <t>34521; 50173</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8612; 18707</t>
+          <t>8244; 18402</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25743; 43599</t>
+          <t>25288; 43350</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37763; 53340</t>
+          <t>37924; 52463</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29079; 42914</t>
+          <t>31046; 45248</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23424; 38529</t>
+          <t>22936; 38309</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>63951; 90924</t>
+          <t>63116; 90189</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>70278; 92242</t>
+          <t>70759; 92225</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>66198; 86648</t>
+          <t>68805; 90021</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117758</t>
+          <t>132316</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>108262</t>
+          <t>120111</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>226020</t>
+          <t>252427</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>46445; 68865</t>
+          <t>45632; 68392</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>149176; 181649</t>
+          <t>146400; 181897</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>107727; 135418</t>
+          <t>106898; 135360</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>101920; 132688</t>
+          <t>115781; 146970</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>51379; 70627</t>
+          <t>50824; 69211</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>125526; 158211</t>
+          <t>123411; 153519</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>109543; 136873</t>
+          <t>109229; 136949</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>95708; 120943</t>
+          <t>106555; 133540</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>101500; 133121</t>
+          <t>103625; 132591</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>284961; 331171</t>
+          <t>281031; 329930</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>226554; 266569</t>
+          <t>224871; 263315</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>207018; 248835</t>
+          <t>230300; 272390</t>
         </is>
       </c>
     </row>
